--- a/tame_output/ON/bt/strategyON_20240206.xlsx
+++ b/tame_output/ON/bt/strategyON_20240206.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,16 +926,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>127.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,16 +1400,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.0%</t>
+          <t>121.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1864"/>
+  <dimension ref="A1:G1865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.301177450802885</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44433,6 +44433,29 @@
       </c>
       <c r="G1864" t="n">
         <v>4.470308232811921</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="2" t="n">
+        <v>45327</v>
+      </c>
+      <c r="B1865" t="n">
+        <v>3.304788296834766</v>
+      </c>
+      <c r="C1865" t="n">
+        <v>3.110625952415132</v>
+      </c>
+      <c r="D1865" t="n">
+        <v>1.640279549362817</v>
+      </c>
+      <c r="E1865" t="n">
+        <v>3.766381347846512</v>
+      </c>
+      <c r="F1865" t="n">
+        <v>2.258112854780415</v>
+      </c>
+      <c r="G1865" t="n">
+        <v>4.465493665283382</v>
       </c>
     </row>
   </sheetData>
